--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484380_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484380_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.165</v>
+        <v>4.5782</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8768</v>
+        <v>3.2901</v>
       </c>
       <c r="F2" t="n">
         <v>1.2882</v>
@@ -610,10 +610,10 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.93</v>
+        <v>0.3432</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8724</v>
+        <v>0.2856</v>
       </c>
       <c r="U2" t="n">
         <v>0.0576</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6973</v>
+        <v>3.3997</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9558</v>
+        <v>2.8644</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6531</v>
+        <v>0.5353</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0345</v>
+        <v>6.0514</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2796</v>
+        <v>2.9095</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7548</v>
+        <v>3.1419</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1826</v>
+        <v>4.9981</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4106</v>
+        <v>2.3945</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5931999999999999</v>
+        <v>2.6036</v>
       </c>
       <c r="M3" t="n">
-        <v>2.217</v>
+        <v>1.0533</v>
       </c>
       <c r="N3" t="n">
-        <v>0.869</v>
+        <v>0.515</v>
       </c>
       <c r="O3" t="n">
-        <v>1.348</v>
+        <v>0.5383</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1651</v>
+        <v>-1.3978</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0384</v>
+        <v>-0.4222</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1267</v>
+        <v>-0.9756</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
         <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4753</v>
+        <v>2.9346</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0762</v>
+        <v>-0.8547</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3991</v>
+        <v>3.7893</v>
       </c>
       <c r="G4" t="n">
-        <v>6.0514</v>
+        <v>2.0345</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9095</v>
+        <v>1.2796</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1419</v>
+        <v>0.7548</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9981</v>
+        <v>-0.1826</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3945</v>
+        <v>0.4106</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6036</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0533</v>
+        <v>2.217</v>
       </c>
       <c r="N4" t="n">
-        <v>0.515</v>
+        <v>0.869</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5383</v>
+        <v>1.348</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3222</v>
+        <v>0.0722</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2105</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1117</v>
+        <v>0.0095</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W4" t="n">
         <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9807</v>
+        <v>1.6834</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2497</v>
+        <v>1.0068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.731</v>
+        <v>0.6766</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9671</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.038</v>
+        <v>-0.2593</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5147</v>
+        <v>0.2718</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4767</v>
+        <v>-0.5311</v>
       </c>
       <c r="V5" t="n">
         <v>2.7145</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1639</v>
+        <v>1.3081</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4521</v>
+        <v>-0.5009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7118</v>
+        <v>1.809</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3865</v>
+        <v>2.7366</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8071</v>
+        <v>2.2789</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5794</v>
+        <v>0.4578</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5178</v>
+        <v>1.7337</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4773</v>
+        <v>1.0054</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8687</v>
+        <v>1.0029</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3298</v>
+        <v>1.2735</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>-0.2706</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6956</v>
+        <v>-0.2098</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5519</v>
+        <v>-0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8563</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9414</v>
+        <v>-1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.1329</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9424</v>
+        <v>-1.8413</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8107</v>
+        <v>2.9742</v>
       </c>
       <c r="G7" t="n">
         <v>1.4703</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0622</v>
+        <v>0.3267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0989</v>
+        <v>0.0022</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1611</v>
+        <v>0.3245</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6642</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.9272</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.573</v>
+        <v>-0.9464</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3094</v>
+        <v>1.8736</v>
       </c>
       <c r="G8" t="n">
         <v>0.3381</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1248</v>
+        <v>0.3157</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1602</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9116</v>
+        <v>0.4758</v>
       </c>
       <c r="V8" t="n">
         <v>0.6642</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4636</v>
+        <v>0.3555</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1275</v>
+        <v>-0.438</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5912</v>
+        <v>0.7935</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7366</v>
+        <v>2.3865</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2789</v>
+        <v>1.8071</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4578</v>
+        <v>0.5794</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7337</v>
+        <v>1.5178</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0054</v>
+        <v>1.4773</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7284</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0029</v>
+        <v>0.8687</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2735</v>
+        <v>0.3298</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2706</v>
+        <v>0.5389</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0544</v>
+        <v>-0.1128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1465</v>
+        <v>-0.7746</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3827</v>
+        <v>-0.3361</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2349</v>
+        <v>-0.1337</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1479</v>
+        <v>-0.2023</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4675</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0847</v>
+        <v>0.1314</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2663</v>
+        <v>0.2118</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2436</v>
+        <v>-1.9628</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.565</v>
+        <v>-3.8485</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3214</v>
+        <v>1.8856</v>
       </c>
       <c r="G11" t="n">
         <v>-2.277</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3106</v>
+        <v>0.5915</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3798</v>
+        <v>0.0964</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9308</v>
+        <v>0.495</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1438</v>
+        <v>-2.0155</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4688</v>
+        <v>-1.3677</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.675</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6365</v>
@@ -1390,13 +1390,13 @@
         <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7027</v>
+        <v>-0.5743</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5211</v>
+        <v>-0.4939</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8411</v>
+        <v>-2.1583</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3904</v>
+        <v>-1.9255</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4507</v>
+        <v>-0.2328</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7443</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4642</v>
+        <v>-0.7814</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5309</v>
+        <v>-0.0659</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9333</v>
+        <v>-0.7154</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6093</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.939399999999999</v>
+        <v>9.846900000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.603</v>
+        <v>-4.695400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>14.5423</v>
+        <v>14.5425</v>
       </c>
       <c r="G14" t="n">
         <v>11.16</v>
@@ -1546,13 +1546,13 @@
         <v>15.6272</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4627</v>
+        <v>-1.5547</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6176999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8449</v>
+        <v>-1.845</v>
       </c>
       <c r="V14" t="n">
         <v>1.2187</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6157</v>
+        <v>3.1322</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8268</v>
+        <v>1.0179</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7889</v>
+        <v>2.1143</v>
       </c>
       <c r="G15" t="n">
         <v>0.6597</v>
@@ -1624,13 +1624,13 @@
         <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6472</v>
+        <v>0.1637</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7651</v>
+        <v>-0.0438</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1179</v>
+        <v>0.2075</v>
       </c>
       <c r="V15" t="n">
         <v>0.9414</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2871</v>
+        <v>1.1756</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0605</v>
+        <v>0.9594</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2267</v>
+        <v>0.2162</v>
       </c>
       <c r="G16" t="n">
         <v>-2.26</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1798</v>
+        <v>1.0682</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2631</v>
+        <v>1.1619</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0833</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4188</v>
+        <v>0.909</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6835</v>
+        <v>0.5593</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1023</v>
+        <v>0.3497</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1161</v>
+        <v>-0.5139</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4651</v>
+        <v>2.2776</v>
       </c>
       <c r="I17" t="n">
-        <v>1.349</v>
+        <v>-2.7915</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3784</v>
+        <v>0.7196</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5107</v>
+        <v>2.7015</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8891</v>
+        <v>-1.9818</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4945</v>
+        <v>-1.2336</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0456</v>
+        <v>-0.4239</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5401</v>
+        <v>-0.8097</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2465</v>
+        <v>0.595</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0851</v>
+        <v>0.5744</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1613</v>
+        <v>0.0206</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1038</v>
+        <v>0.765</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0537</v>
+        <v>-0.5823</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0501</v>
+        <v>1.3474</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5139</v>
+        <v>-0.1161</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2776</v>
+        <v>-1.4651</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7915</v>
+        <v>1.349</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7196</v>
+        <v>0.3784</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7015</v>
+        <v>-1.5107</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9818</v>
+        <v>1.8891</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2336</v>
+        <v>-0.4945</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4239</v>
+        <v>0.0456</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8097</v>
+        <v>-0.5401</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2102</v>
+        <v>0.0998</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0689</v>
+        <v>0.016</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.279</v>
+        <v>0.0838</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6158</v>
+        <v>0.7169</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7153</v>
+        <v>-0.7698</v>
       </c>
       <c r="G19" t="n">
         <v>0.7923</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0639</v>
+        <v>-0.0172</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0467</v>
+        <v>0.0544</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0171</v>
+        <v>-0.0716</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4196</v>
+        <v>-0.3185</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8196</v>
+        <v>-0.7185</v>
       </c>
       <c r="F20" t="n">
         <v>0.4</v>
@@ -2014,10 +2014,10 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.586</v>
+        <v>-0.4849</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1732</v>
+        <v>-1.4779</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0398</v>
+        <v>-2.3432</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8667</v>
+        <v>0.8653</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9419</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2999</v>
+        <v>-0.0048</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3247</v>
+        <v>0.0214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0248</v>
+        <v>-0.0262</v>
       </c>
       <c r="V21" t="n">
         <v>0.6642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2847</v>
+        <v>-1.8895</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6008</v>
+        <v>-1.0952</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7943</v>
       </c>
       <c r="G22" t="n">
         <v>0.4707</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0094</v>
+        <v>0.3859</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4153</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4059</v>
+        <v>0.2956</v>
       </c>
       <c r="V22" t="n">
         <v>-2.16</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.556</v>
+        <v>-2.8903</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.732</v>
+        <v>-3.3387</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1761</v>
+        <v>0.4484</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8987</v>
@@ -2248,13 +2248,13 @@
         <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7567</v>
+        <v>0.4224</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8118</v>
+        <v>0.2052</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0551</v>
+        <v>0.2173</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.817</v>
+        <v>-3.3695</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6055</v>
+        <v>-3.5044</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7885</v>
+        <v>0.1349</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3514</v>
@@ -2326,13 +2326,13 @@
         <v>2.5395</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2534</v>
+        <v>0.7009</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2116</v>
+        <v>-0.1105</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4651</v>
+        <v>0.8114</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3283</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0147</v>
+        <v>-4.2031</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.6179</v>
+        <v>-6.2135</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6032</v>
+        <v>2.0104</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3623</v>
@@ -2404,13 +2404,13 @@
         <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5585</v>
+        <v>0.2532</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1457</v>
+        <v>0.2588</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4128</v>
+        <v>-0.0056</v>
       </c>
       <c r="V25" t="n">
         <v>0.6642</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.939300000000001</v>
+        <v>-8.219899999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-14.5423</v>
       </c>
       <c r="F26" t="n">
-        <v>5.6032</v>
+        <v>6.3225</v>
       </c>
       <c r="G26" t="n">
         <v>-11.1599</v>
@@ -2482,13 +2482,13 @@
         <v>16.6043</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4625</v>
+        <v>3.1822</v>
       </c>
       <c r="T26" t="n">
         <v>1.845</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6179000000000001</v>
+        <v>1.3373</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2185</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484380_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484380_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,7 +895,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -938,17 +963,22 @@
       </c>
       <c r="X6" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,6 +1046,11 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1026,74 +1061,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9272</v>
+        <v>0.921</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9464</v>
+        <v>0.921</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8736</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3381</v>
+        <v>0.921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5815</v>
+        <v>0.921</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2434</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1672</v>
+        <v>0.921</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0054</v>
+        <v>0.921</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8290999999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4239</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4052</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3157</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1602</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4758</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1104,7 +1144,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1172,480 +1212,511 @@
       </c>
       <c r="X9" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3361</v>
+        <v>0.0063</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1337</v>
+        <v>-1.8673</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2023</v>
+        <v>1.8736</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4675</v>
+        <v>-0.5829</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1668</v>
+        <v>-0.3395</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6994</v>
+        <v>-0.2434</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0533</v>
+        <v>0.2463</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3482</v>
+        <v>0.0844</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2949</v>
+        <v>0.1619</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4142</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8186</v>
+        <v>-0.4239</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4045</v>
+        <v>-0.4052</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1314</v>
+        <v>0.3157</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0805</v>
+        <v>-0.1602</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2118</v>
+        <v>0.4758</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9628</v>
+        <v>-0.3361</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8485</v>
+        <v>-0.1337</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8856</v>
+        <v>-0.2023</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.277</v>
+        <v>-0.4675</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0607</v>
+        <v>-2.1668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2163</v>
+        <v>1.6994</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2101</v>
+        <v>-0.0533</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.2644</v>
+        <v>-1.3482</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0543</v>
+        <v>1.2949</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9330000000000001</v>
+        <v>-0.4142</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2037</v>
+        <v>-0.8186</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2706</v>
+        <v>0.4045</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5915</v>
+        <v>0.1314</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0964</v>
+        <v>-0.0805</v>
       </c>
       <c r="U11" t="n">
-        <v>0.495</v>
+        <v>0.2118</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0155</v>
+        <v>-1.9628</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3677</v>
+        <v>-3.8485</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6477000000000001</v>
+        <v>1.8856</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6365</v>
+        <v>-2.277</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7332</v>
+        <v>-2.0607</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9033</v>
+        <v>-0.2163</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2873</v>
+        <v>-3.2101</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0205</v>
+        <v>-3.2644</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3077</v>
+        <v>0.0543</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3492</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7536</v>
+        <v>1.2037</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4045</v>
+        <v>-0.2706</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5743</v>
+        <v>0.5915</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0805</v>
+        <v>0.0964</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4939</v>
+        <v>0.495</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1583</v>
+        <v>-2.0155</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9255</v>
+        <v>-1.3677</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2328</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7443</v>
+        <v>-1.6365</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2858</v>
+        <v>-0.7332</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4585</v>
+        <v>-0.9033</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8595</v>
+        <v>-1.2873</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2673</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1152</v>
+        <v>-0.3492</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6935</v>
+        <v>-0.7536</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8087</v>
+        <v>0.4045</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7814</v>
+        <v>-0.5743</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0659</v>
+        <v>-0.0805</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7154</v>
+        <v>-0.4939</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.846900000000002</v>
+        <v>-2.1583</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.695400000000001</v>
+        <v>-1.9255</v>
       </c>
       <c r="F14" t="n">
-        <v>14.5425</v>
+        <v>-0.2328</v>
       </c>
       <c r="G14" t="n">
-        <v>11.16</v>
+        <v>-1.7443</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0475</v>
+        <v>-1.2858</v>
       </c>
       <c r="I14" t="n">
-        <v>10.1126</v>
+        <v>-0.4585</v>
       </c>
       <c r="J14" t="n">
-        <v>5.967200000000001</v>
+        <v>-1.8595</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9159</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.051499999999999</v>
+        <v>-1.2673</v>
       </c>
       <c r="M14" t="n">
-        <v>5.192699999999999</v>
+        <v>0.1152</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8683000000000003</v>
+        <v>-0.6935</v>
       </c>
       <c r="O14" t="n">
-        <v>6.061199999999999</v>
+        <v>0.8087</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9768</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.6039</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>15.6272</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5547</v>
+        <v>-0.7814</v>
       </c>
       <c r="T14" t="n">
-        <v>0.29</v>
+        <v>-0.0659</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.845</v>
+        <v>-0.7154</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2187</v>
+        <v>-0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>5.651199999999999</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.4327</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1322</v>
+        <v>9.847000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0179</v>
+        <v>-4.6953</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1143</v>
+        <v>14.5425</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6597</v>
+        <v>11.16</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9437</v>
+        <v>1.0475</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2841</v>
+        <v>10.1126</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8198</v>
+        <v>5.967299999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6984</v>
+        <v>1.915899999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>4.051499999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1601</v>
+        <v>5.192699999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2454</v>
+        <v>-0.8683000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4054</v>
+        <v>6.061199999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-0.9768</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-16.6039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>15.6272</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1637</v>
+        <v>-1.5547</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0438</v>
+        <v>0.2899999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2075</v>
+        <v>-1.845</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9414</v>
+        <v>1.2187</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>5.651199999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-4.4327</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1756</v>
+        <v>3.1322</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9594</v>
+        <v>1.0179</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2162</v>
+        <v>2.1143</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.26</v>
+        <v>0.6597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2745</v>
+        <v>0.9437</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.5345</v>
+        <v>-0.2841</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.0305</v>
+        <v>0.8198</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6382</v>
+        <v>0.6984</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.6688</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2295</v>
+        <v>-0.1601</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3638</v>
+        <v>0.2454</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1342</v>
+        <v>-0.4054</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0682</v>
+        <v>0.1637</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1619</v>
+        <v>-0.0438</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.2075</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>0.9414</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.909</v>
+        <v>1.1756</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5593</v>
+        <v>0.9594</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3497</v>
+        <v>0.2162</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5139</v>
+        <v>-2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2776</v>
+        <v>0.2745</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7915</v>
+        <v>-2.5345</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7196</v>
+        <v>-2.0305</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7015</v>
+        <v>0.6382</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9818</v>
+        <v>-2.6688</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2336</v>
+        <v>-0.2295</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4239</v>
+        <v>-0.3638</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8097</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.595</v>
+        <v>1.0682</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5744</v>
+        <v>1.1619</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0206</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. BALLUS TORRAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.765</v>
+        <v>0.602</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5823</v>
+        <v>0.2523</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3474</v>
+        <v>0.3497</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1161</v>
+        <v>-0.8209</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4651</v>
+        <v>1.9706</v>
       </c>
       <c r="I18" t="n">
-        <v>1.349</v>
+        <v>-2.7915</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3784</v>
+        <v>0.4127</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5107</v>
+        <v>2.3945</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8891</v>
+        <v>-1.9818</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4945</v>
+        <v>-1.2336</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0456</v>
+        <v>-0.4239</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5401</v>
+        <v>-0.8097</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0998</v>
+        <v>0.595</v>
       </c>
       <c r="T18" t="n">
-        <v>0.016</v>
+        <v>0.5744</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0838</v>
+        <v>0.0206</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ BUFI</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0529</v>
+        <v>0.458</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7169</v>
+        <v>-0.8893</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7698</v>
+        <v>1.3474</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7923</v>
+        <v>-0.4231</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1384</v>
+        <v>-1.7721</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9307</v>
+        <v>1.349</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6625</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0013</v>
+        <v>-1.8176</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6613</v>
+        <v>1.8891</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1298</v>
+        <v>-0.4945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1397</v>
+        <v>0.0456</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2694</v>
+        <v>-0.5401</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0172</v>
+        <v>0.0998</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0544</v>
+        <v>0.016</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0716</v>
+        <v>0.0838</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VÁZQUEZ MARESMA</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3185</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7185</v>
+        <v>0.307</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3617</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2589</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6206</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6413</v>
+        <v>0.307</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2793</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4849</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3831</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1018</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4779</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3432</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8653</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9419</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0806</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0225</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3879</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6344</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0223</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.554</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5538</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0048</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0214</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0262</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>C. FERNANDEZ BUFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8895</v>
+        <v>-0.0529</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0952</v>
+        <v>0.7169</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7943</v>
+        <v>-0.7698</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4707</v>
+        <v>0.7923</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7005</v>
+        <v>-0.1384</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2298</v>
+        <v>0.9307</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4907</v>
+        <v>0.6625</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4502</v>
+        <v>0.0013</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.6613</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.02</v>
+        <v>0.1298</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2502</v>
+        <v>-0.1397</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2702</v>
+        <v>0.2694</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3859</v>
+        <v>-0.0172</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0544</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2956</v>
+        <v>-0.0716</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.16</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>E. VAZQUEZ MARESMA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8903</v>
+        <v>-0.3185</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3387</v>
+        <v>-0.7185</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4484</v>
+        <v>0.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8987</v>
+        <v>0.3617</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1072</v>
+        <v>-0.2589</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7915</v>
+        <v>0.6206</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5904</v>
+        <v>0.6413</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3914</v>
+        <v>0.0205</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9818</v>
+        <v>0.6208</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3083</v>
+        <v>-0.2795</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4986</v>
+        <v>-0.2793</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8097</v>
+        <v>-0.0002</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4224</v>
+        <v>-0.4849</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2052</v>
+        <v>-0.3831</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2173</v>
+        <v>-0.1018</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3695</v>
+        <v>-1.4779</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5044</v>
+        <v>-2.3432</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1349</v>
+        <v>0.8653</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3514</v>
+        <v>-1.9419</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2781</v>
+        <v>0.0806</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6295</v>
+        <v>-2.0225</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3541</v>
+        <v>-1.3879</v>
       </c>
       <c r="K24" t="n">
-        <v>0.926</v>
+        <v>0.6344</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2801</v>
+        <v>-2.0223</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9973</v>
+        <v>-0.554</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.648</v>
+        <v>-0.5538</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3494</v>
+        <v>-0.0002</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7009</v>
+        <v>-0.0048</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1105</v>
+        <v>0.0214</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8114</v>
+        <v>-0.0262</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3283</v>
+        <v>0.6642</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1097</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2031</v>
+        <v>-1.8895</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2135</v>
+        <v>-1.0952</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0104</v>
+        <v>-0.7943</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3623</v>
+        <v>0.4707</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.633</v>
+        <v>0.7005</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2706</v>
+        <v>-0.2298</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.5421</v>
+        <v>0.4907</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.083</v>
+        <v>0.4502</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5409</v>
+        <v>0.0405</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1798</v>
+        <v>-0.02</v>
       </c>
       <c r="N25" t="n">
-        <v>0.45</v>
+        <v>0.2502</v>
       </c>
       <c r="O25" t="n">
         <v>-0.2702</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2532</v>
+        <v>0.3859</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2588</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0056</v>
+        <v>0.2956</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6642</v>
+        <v>-2.16</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X25" t="n">
-        <v>0.6642</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,318 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-2.8903</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.3387</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.8987</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.1072</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.7915</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.5904</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.3083</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.4986</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C. HOMS LORENZO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.3695</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.5044</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.3514</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.6295</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.3541</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.2801</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.9973</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1105</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.1097</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-4.2031</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-6.2135</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.0104</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-3.3623</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3.633</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3.5421</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-4.083</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.2702</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2532</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484380_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>-8.219899999999999</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E29" t="n">
         <v>-14.5423</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F29" t="n">
         <v>6.3225</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G29" t="n">
         <v>-11.1599</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H29" t="n">
         <v>-1.0476</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I29" t="n">
         <v>-10.1125</v>
       </c>
-      <c r="J26" t="n">
-        <v>-5.1927</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.8681999999999999</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="J29" t="n">
+        <v>-5.192600000000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8682999999999996</v>
+      </c>
+      <c r="L29" t="n">
         <v>-6.0608</v>
       </c>
-      <c r="M26" t="n">
-        <v>-5.9672</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="M29" t="n">
+        <v>-5.967200000000001</v>
+      </c>
+      <c r="N29" t="n">
         <v>-1.9159</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O29" t="n">
         <v>-4.0515</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>0.9767999999999997</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-15.6272</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>16.6043</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S29" t="n">
         <v>3.1822</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>1.845</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U29" t="n">
         <v>1.3373</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V29" t="n">
         <v>-1.2185</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>4.4326</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>-5.6512</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
